--- a/docs/baseline/output/05_검진_예약접수_SP계약서.xlsx
+++ b/docs/baseline/output/05_검진_예약접수_SP계약서.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2433" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2433" uniqueCount="474">
   <si>
     <t>외부 호출 Stored Procedure 16개</t>
   </si>
@@ -1050,6 +1050,9 @@
   </si>
   <si>
     <t>304</t>
+  </si>
+  <si>
+    <t>CutoffPassed</t>
   </si>
   <si>
     <t>해당 시간대의 마감시간이 지났습니다.</t>
@@ -10444,10 +10447,10 @@
         <v>344</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>235</v>
+        <v>345</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>214</v>
@@ -10455,13 +10458,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>214</v>
@@ -10469,13 +10472,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>192</v>
@@ -10483,13 +10486,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>214</v>
@@ -10497,13 +10500,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>75</v>
@@ -10511,13 +10514,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>75</v>
@@ -10525,13 +10528,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>213</v>
@@ -10539,13 +10542,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>213</v>
@@ -10553,55 +10556,55 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>212</v>
@@ -10609,13 +10612,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>192</v>
@@ -10623,13 +10626,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>212</v>
@@ -10637,13 +10640,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>212</v>
@@ -10651,13 +10654,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>208</v>
@@ -10665,13 +10668,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>75</v>
@@ -10679,27 +10682,27 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>272</v>
@@ -10707,13 +10710,13 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>272</v>
@@ -10721,13 +10724,13 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>273</v>
@@ -10755,12 +10758,12 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -10769,7 +10772,7 @@
         <v>3</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>74</v>
@@ -10783,7 +10786,7 @@
         <v>77</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>4</v>
@@ -10791,7 +10794,7 @@
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -10800,7 +10803,7 @@
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>78</v>
@@ -10809,7 +10812,7 @@
         <v>79</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -10818,7 +10821,7 @@
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>82</v>
@@ -10827,7 +10830,7 @@
         <v>83</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -10836,7 +10839,7 @@
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>85</v>
@@ -10845,7 +10848,7 @@
         <v>86</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -10854,7 +10857,7 @@
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>88</v>
@@ -10863,7 +10866,7 @@
         <v>89</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -10872,7 +10875,7 @@
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>188</v>
@@ -10881,7 +10884,7 @@
         <v>103</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -10890,16 +10893,16 @@
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>173</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -10908,16 +10911,16 @@
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>175</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -10926,7 +10929,7 @@
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>186</v>
@@ -10935,7 +10938,7 @@
         <v>103</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -10944,7 +10947,7 @@
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>182</v>
@@ -10953,7 +10956,7 @@
         <v>120</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -10962,7 +10965,7 @@
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>233</v>
@@ -10971,7 +10974,7 @@
         <v>103</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -10980,7 +10983,7 @@
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>234</v>
@@ -10989,7 +10992,7 @@
         <v>184</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -10998,7 +11001,7 @@
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>235</v>
@@ -11007,7 +11010,7 @@
         <v>103</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -11016,16 +11019,16 @@
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>103</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -11034,7 +11037,7 @@
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>241</v>
@@ -11043,7 +11046,7 @@
         <v>173</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -11052,7 +11055,7 @@
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>242</v>
@@ -11061,7 +11064,7 @@
         <v>175</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -11069,7 +11072,7 @@
         <v>91</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4</v>
@@ -11077,7 +11080,7 @@
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -11086,7 +11089,7 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>92</v>
@@ -11095,7 +11098,7 @@
         <v>93</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -11104,7 +11107,7 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>82</v>
@@ -11113,7 +11116,7 @@
         <v>83</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -11122,7 +11125,7 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>238</v>
@@ -11131,7 +11134,7 @@
         <v>103</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -11140,7 +11143,7 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>239</v>
@@ -11149,7 +11152,7 @@
         <v>173</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -11158,7 +11161,7 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>240</v>
@@ -11167,7 +11170,7 @@
         <v>83</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -11176,7 +11179,7 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>241</v>
@@ -11185,7 +11188,7 @@
         <v>173</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -11194,7 +11197,7 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>242</v>
@@ -11203,7 +11206,7 @@
         <v>175</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -11211,7 +11214,7 @@
         <v>96</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>4</v>
@@ -11219,7 +11222,7 @@
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -11228,7 +11231,7 @@
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>92</v>
@@ -11237,7 +11240,7 @@
         <v>93</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -11246,7 +11249,7 @@
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>82</v>
@@ -11255,7 +11258,7 @@
         <v>83</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -11264,7 +11267,7 @@
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>244</v>
@@ -11273,7 +11276,7 @@
         <v>89</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -11282,7 +11285,7 @@
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>245</v>
@@ -11291,7 +11294,7 @@
         <v>120</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -11300,7 +11303,7 @@
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>246</v>
@@ -11309,7 +11312,7 @@
         <v>220</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -11318,7 +11321,7 @@
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>247</v>
@@ -11327,7 +11330,7 @@
         <v>89</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -11335,7 +11338,7 @@
         <v>97</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>4</v>
@@ -11343,7 +11346,7 @@
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
       <c r="F34" s="5" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -11352,7 +11355,7 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>92</v>
@@ -11361,7 +11364,7 @@
         <v>93</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -11370,7 +11373,7 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>82</v>
@@ -11379,7 +11382,7 @@
         <v>83</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -11388,7 +11391,7 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>99</v>
@@ -11397,7 +11400,7 @@
         <v>93</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -11406,7 +11409,7 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>102</v>
@@ -11415,7 +11418,7 @@
         <v>103</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -11424,7 +11427,7 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>105</v>
@@ -11433,7 +11436,7 @@
         <v>103</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -11442,7 +11445,7 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>107</v>
@@ -11451,7 +11454,7 @@
         <v>103</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -11460,7 +11463,7 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>109</v>
@@ -11469,7 +11472,7 @@
         <v>103</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -11478,7 +11481,7 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>111</v>
@@ -11487,7 +11490,7 @@
         <v>103</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -11496,7 +11499,7 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>113</v>
@@ -11505,7 +11508,7 @@
         <v>103</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -11514,7 +11517,7 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>115</v>
@@ -11523,7 +11526,7 @@
         <v>103</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -11532,7 +11535,7 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>117</v>
@@ -11541,7 +11544,7 @@
         <v>103</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -11550,7 +11553,7 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>249</v>
@@ -11559,7 +11562,7 @@
         <v>89</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -11568,7 +11571,7 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>244</v>
@@ -11577,7 +11580,7 @@
         <v>89</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -11586,7 +11589,7 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>245</v>
@@ -11595,7 +11598,7 @@
         <v>120</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -11604,7 +11607,7 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>250</v>
@@ -11613,7 +11616,7 @@
         <v>103</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -11622,7 +11625,7 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>251</v>
@@ -11631,7 +11634,7 @@
         <v>103</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -11640,7 +11643,7 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>236</v>
@@ -11649,7 +11652,7 @@
         <v>103</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -11658,7 +11661,7 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>241</v>
@@ -11667,7 +11670,7 @@
         <v>173</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -11676,7 +11679,7 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>242</v>
@@ -11685,7 +11688,7 @@
         <v>175</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
   </sheetData>

--- a/docs/baseline/output/05_검진_예약접수_SP계약서.xlsx
+++ b/docs/baseline/output/05_검진_예약접수_SP계약서.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2433" uniqueCount="474">
   <si>
-    <t>외부 호출 Stored Procedure 16개</t>
+    <t>외부 호출 Stored Procedure 20개</t>
   </si>
   <si>
     <t>ID</t>

--- a/docs/baseline/output/05_검진_예약접수_SP계약서.xlsx
+++ b/docs/baseline/output/05_검진_예약접수_SP계약서.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2433" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2433" uniqueCount="475">
   <si>
     <t>외부 호출 Stored Procedure 20개</t>
   </si>
@@ -380,55 +380,58 @@
     <t>NVARCHAR(100)</t>
   </si>
   <si>
+    <t>포함검색</t>
+  </si>
+  <si>
+    <t>@성명</t>
+  </si>
+  <si>
+    <t>@주민번호</t>
+  </si>
+  <si>
+    <t>VARCHAR(13)</t>
+  </si>
+  <si>
+    <t>C#에서 - 제거 후 정확검색</t>
+  </si>
+  <si>
+    <t>@생년월일</t>
+  </si>
+  <si>
+    <t>VARCHAR(8)</t>
+  </si>
+  <si>
     <t>정확검색</t>
   </si>
   <si>
-    <t>@성명</t>
+    <t>@휴대전화</t>
+  </si>
+  <si>
+    <t>- 제거 후 정확검색</t>
+  </si>
+  <si>
+    <t>@시작일</t>
+  </si>
+  <si>
+    <t>시작일 포함</t>
+  </si>
+  <si>
+    <t>@종료일</t>
+  </si>
+  <si>
+    <t>종료일 포함</t>
+  </si>
+  <si>
+    <t>@상태코드</t>
+  </si>
+  <si>
+    <t>CHAR(3)</t>
+  </si>
+  <si>
+    <t>NULL / RSV / RCP / CNR / CNC</t>
   </si>
   <si>
     <t>접두검색</t>
-  </si>
-  <si>
-    <t>@주민번호</t>
-  </si>
-  <si>
-    <t>VARCHAR(13)</t>
-  </si>
-  <si>
-    <t>C#에서 - 제거 후 정확검색</t>
-  </si>
-  <si>
-    <t>@생년월일</t>
-  </si>
-  <si>
-    <t>VARCHAR(8)</t>
-  </si>
-  <si>
-    <t>@휴대전화</t>
-  </si>
-  <si>
-    <t>- 제거 후 정확검색</t>
-  </si>
-  <si>
-    <t>@시작일</t>
-  </si>
-  <si>
-    <t>시작일 포함</t>
-  </si>
-  <si>
-    <t>@종료일</t>
-  </si>
-  <si>
-    <t>종료일 포함</t>
-  </si>
-  <si>
-    <t>@상태코드</t>
-  </si>
-  <si>
-    <t>CHAR(3)</t>
-  </si>
-  <si>
-    <t>NULL / RSV / RCP / CNR / CNC</t>
   </si>
   <si>
     <t>@대상테이블</t>
@@ -2657,7 +2660,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2668,16 +2671,16 @@
         <v>3</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>124</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>125</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>100</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2688,16 +2691,16 @@
         <v>4</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>100</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2711,7 +2714,7 @@
         <v>129</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>100</v>
@@ -2833,7 +2836,7 @@
         <v>100</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2853,7 +2856,7 @@
         <v>100</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2882,10 +2885,10 @@
         <v>1</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>80</v>
@@ -2900,7 +2903,7 @@
         <v>2</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>93</v>
@@ -2954,10 +2957,10 @@
         <v>3</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>100</v>
@@ -2972,7 +2975,7 @@
         <v>4</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>89</v>
@@ -3152,7 +3155,7 @@
         <v>1</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>103</v>
@@ -3206,10 +3209,10 @@
         <v>4</v>
       </c>
       <c r="C53" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D53" s="5" t="s">
         <v>124</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>125</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>80</v>
@@ -3227,7 +3230,7 @@
         <v>129</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>100</v>
@@ -3242,10 +3245,10 @@
         <v>6</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E55" s="6" t="s">
         <v>100</v>
@@ -3260,10 +3263,10 @@
         <v>7</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>100</v>
@@ -3278,7 +3281,7 @@
         <v>8</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>89</v>
@@ -3296,10 +3299,10 @@
         <v>9</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>100</v>
@@ -3314,10 +3317,10 @@
         <v>10</v>
       </c>
       <c r="C59" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D59" s="5" t="s">
         <v>151</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>150</v>
       </c>
       <c r="E59" s="6" t="s">
         <v>100</v>
@@ -3332,10 +3335,10 @@
         <v>11</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>100</v>
@@ -3350,7 +3353,7 @@
         <v>12</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>103</v>
@@ -3368,7 +3371,7 @@
         <v>13</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>103</v>
@@ -3386,10 +3389,10 @@
         <v>14</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E63" s="6" t="s">
         <v>80</v>
@@ -3422,10 +3425,10 @@
         <v>2</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>80</v>
@@ -3476,10 +3479,10 @@
         <v>5</v>
       </c>
       <c r="C68" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D68" s="3" t="s">
         <v>124</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>125</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>80</v>
@@ -3497,7 +3500,7 @@
         <v>129</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>100</v>
@@ -3512,10 +3515,10 @@
         <v>7</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>100</v>
@@ -3530,10 +3533,10 @@
         <v>8</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>100</v>
@@ -3548,7 +3551,7 @@
         <v>9</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>89</v>
@@ -3566,10 +3569,10 @@
         <v>10</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>100</v>
@@ -3584,10 +3587,10 @@
         <v>11</v>
       </c>
       <c r="C74" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D74" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>100</v>
@@ -3602,10 +3605,10 @@
         <v>12</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>100</v>
@@ -3620,7 +3623,7 @@
         <v>13</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>103</v>
@@ -3638,10 +3641,10 @@
         <v>14</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>80</v>
@@ -3674,7 +3677,7 @@
         <v>2</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D79" s="5" t="s">
         <v>89</v>
@@ -3854,10 +3857,10 @@
         <v>12</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E89" s="6" t="s">
         <v>80</v>
@@ -3890,10 +3893,10 @@
         <v>2</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E91" s="4" t="s">
         <v>80</v>
@@ -4070,10 +4073,10 @@
         <v>12</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E101" s="4" t="s">
         <v>80</v>
@@ -4106,10 +4109,10 @@
         <v>2</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E103" s="6" t="s">
         <v>80</v>
@@ -4124,10 +4127,10 @@
         <v>3</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>80</v>
@@ -4160,10 +4163,10 @@
         <v>2</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E106" s="4" t="s">
         <v>80</v>
@@ -4178,10 +4181,10 @@
         <v>3</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E107" s="4" t="s">
         <v>80</v>
@@ -4214,10 +4217,10 @@
         <v>2</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E109" s="6" t="s">
         <v>80</v>
@@ -4358,10 +4361,10 @@
         <v>10</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E117" s="6" t="s">
         <v>80</v>
@@ -4394,10 +4397,10 @@
         <v>2</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E119" s="4" t="s">
         <v>80</v>
@@ -4412,10 +4415,10 @@
         <v>3</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E120" s="4" t="s">
         <v>80</v>
@@ -4430,7 +4433,7 @@
         <v>1</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D121" s="5" t="s">
         <v>83</v>
@@ -4448,7 +4451,7 @@
         <v>2</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D122" s="5" t="s">
         <v>83</v>
@@ -4466,10 +4469,10 @@
         <v>3</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E123" s="6" t="s">
         <v>100</v>
@@ -4484,7 +4487,7 @@
         <v>1</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>83</v>
@@ -4502,7 +4505,7 @@
         <v>2</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D125" s="3" t="s">
         <v>120</v>
@@ -4520,7 +4523,7 @@
         <v>3</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D126" s="3" t="s">
         <v>103</v>
@@ -4538,10 +4541,10 @@
         <v>4</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E127" s="4" t="s">
         <v>100</v>
@@ -4556,7 +4559,7 @@
         <v>1</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D128" s="5" t="s">
         <v>83</v>
@@ -4574,10 +4577,10 @@
         <v>2</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E129" s="6" t="s">
         <v>80</v>
@@ -4592,7 +4595,7 @@
         <v>3</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D130" s="5" t="s">
         <v>120</v>
@@ -4610,7 +4613,7 @@
         <v>4</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D131" s="5" t="s">
         <v>103</v>
@@ -4628,10 +4631,10 @@
         <v>5</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>100</v>
@@ -4646,7 +4649,7 @@
         <v>1</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D133" s="3" t="s">
         <v>83</v>
@@ -4664,10 +4667,10 @@
         <v>2</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E134" s="4" t="s">
         <v>80</v>
@@ -4696,21 +4699,21 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>74</v>
@@ -4724,13 +4727,13 @@
         <v>7</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C3" s="4">
         <v>1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>103</v>
@@ -4744,16 +4747,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C4" s="4">
         <v>2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>80</v>
@@ -4764,16 +4767,16 @@
         <v>7</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C5" s="4">
         <v>3</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>80</v>
@@ -4784,16 +4787,16 @@
         <v>7</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C6" s="4">
         <v>4</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>100</v>
@@ -4804,13 +4807,13 @@
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C7" s="4">
         <v>5</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>79</v>
@@ -4824,13 +4827,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C8" s="4">
         <v>1</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>83</v>
@@ -4844,16 +4847,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C9" s="4">
         <v>2</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>80</v>
@@ -4864,13 +4867,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C10" s="4">
         <v>3</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>120</v>
@@ -4884,16 +4887,16 @@
         <v>7</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C11" s="4">
         <v>4</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>80</v>
@@ -4904,16 +4907,16 @@
         <v>7</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C12" s="4">
         <v>5</v>
       </c>
       <c r="D12" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>80</v>
@@ -4924,13 +4927,13 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C13" s="4">
         <v>6</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>103</v>
@@ -4944,13 +4947,13 @@
         <v>7</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C14" s="4">
         <v>7</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>103</v>
@@ -4964,13 +4967,13 @@
         <v>7</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C15" s="4">
         <v>8</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>103</v>
@@ -4984,16 +4987,16 @@
         <v>7</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C16" s="4">
         <v>9</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>80</v>
@@ -5004,16 +5007,16 @@
         <v>7</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C17" s="4">
         <v>10</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>80</v>
@@ -5024,13 +5027,13 @@
         <v>11</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C18" s="6">
         <v>1</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>103</v>
@@ -5044,16 +5047,16 @@
         <v>11</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C19" s="6">
         <v>2</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>80</v>
@@ -5064,16 +5067,16 @@
         <v>11</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C20" s="6">
         <v>3</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>80</v>
@@ -5084,16 +5087,16 @@
         <v>11</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C21" s="6">
         <v>4</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>100</v>
@@ -5104,13 +5107,13 @@
         <v>11</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C22" s="6">
         <v>5</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>79</v>
@@ -5124,13 +5127,13 @@
         <v>11</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C23" s="6">
         <v>1</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>93</v>
@@ -5144,13 +5147,13 @@
         <v>11</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C24" s="6">
         <v>2</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>120</v>
@@ -5164,13 +5167,13 @@
         <v>11</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C25" s="6">
         <v>3</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>120</v>
@@ -5184,16 +5187,16 @@
         <v>11</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C26" s="6">
         <v>4</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>80</v>
@@ -5204,16 +5207,16 @@
         <v>11</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C27" s="6">
         <v>5</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>80</v>
@@ -5224,16 +5227,16 @@
         <v>11</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C28" s="6">
         <v>6</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>80</v>
@@ -5244,16 +5247,16 @@
         <v>11</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C29" s="6">
         <v>7</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>100</v>
@@ -5264,16 +5267,16 @@
         <v>11</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C30" s="6">
         <v>8</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>100</v>
@@ -5284,16 +5287,16 @@
         <v>11</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C31" s="6">
         <v>9</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>100</v>
@@ -5304,13 +5307,13 @@
         <v>11</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C32" s="6">
         <v>10</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>89</v>
@@ -5324,16 +5327,16 @@
         <v>11</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C33" s="6">
         <v>11</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F33" s="6" t="s">
         <v>100</v>
@@ -5344,13 +5347,13 @@
         <v>14</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C34" s="4">
         <v>1</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>103</v>
@@ -5364,16 +5367,16 @@
         <v>14</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C35" s="4">
         <v>2</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>80</v>
@@ -5384,16 +5387,16 @@
         <v>14</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C36" s="4">
         <v>3</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>80</v>
@@ -5404,16 +5407,16 @@
         <v>14</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C37" s="4">
         <v>4</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>100</v>
@@ -5424,13 +5427,13 @@
         <v>14</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C38" s="4">
         <v>5</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>79</v>
@@ -5444,13 +5447,13 @@
         <v>14</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C39" s="4">
         <v>1</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>93</v>
@@ -5464,13 +5467,13 @@
         <v>14</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C40" s="4">
         <v>2</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>120</v>
@@ -5484,13 +5487,13 @@
         <v>14</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C41" s="4">
         <v>3</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>120</v>
@@ -5504,16 +5507,16 @@
         <v>14</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C42" s="4">
         <v>4</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>80</v>
@@ -5524,16 +5527,16 @@
         <v>14</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C43" s="4">
         <v>5</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>80</v>
@@ -5544,16 +5547,16 @@
         <v>14</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C44" s="4">
         <v>6</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>80</v>
@@ -5564,16 +5567,16 @@
         <v>14</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C45" s="4">
         <v>7</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>100</v>
@@ -5584,16 +5587,16 @@
         <v>14</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C46" s="4">
         <v>8</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>100</v>
@@ -5604,16 +5607,16 @@
         <v>14</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C47" s="4">
         <v>9</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>100</v>
@@ -5624,13 +5627,13 @@
         <v>14</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C48" s="4">
         <v>10</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>89</v>
@@ -5644,16 +5647,16 @@
         <v>14</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C49" s="4">
         <v>11</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>100</v>
@@ -5664,16 +5667,16 @@
         <v>14</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C50" s="4">
         <v>12</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>100</v>
@@ -5684,16 +5687,16 @@
         <v>14</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C51" s="4">
         <v>13</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>100</v>
@@ -5704,13 +5707,13 @@
         <v>14</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C52" s="4">
         <v>14</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>103</v>
@@ -5724,16 +5727,16 @@
         <v>14</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C53" s="4">
         <v>15</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>80</v>
@@ -5744,13 +5747,13 @@
         <v>17</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C54" s="6">
         <v>1</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E54" s="5" t="s">
         <v>103</v>
@@ -5764,16 +5767,16 @@
         <v>17</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C55" s="6">
         <v>2</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>80</v>
@@ -5784,16 +5787,16 @@
         <v>17</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C56" s="6">
         <v>3</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>80</v>
@@ -5804,16 +5807,16 @@
         <v>17</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C57" s="6">
         <v>4</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F57" s="6" t="s">
         <v>100</v>
@@ -5824,13 +5827,13 @@
         <v>17</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C58" s="6">
         <v>5</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E58" s="5" t="s">
         <v>79</v>
@@ -5844,13 +5847,13 @@
         <v>17</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C59" s="6">
         <v>1</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E59" s="5" t="s">
         <v>93</v>
@@ -5864,13 +5867,13 @@
         <v>17</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C60" s="6">
         <v>2</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E60" s="5" t="s">
         <v>120</v>
@@ -5884,13 +5887,13 @@
         <v>17</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C61" s="6">
         <v>3</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E61" s="5" t="s">
         <v>120</v>
@@ -5904,16 +5907,16 @@
         <v>17</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C62" s="6">
         <v>4</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>80</v>
@@ -5924,16 +5927,16 @@
         <v>17</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C63" s="6">
         <v>5</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F63" s="6" t="s">
         <v>80</v>
@@ -5944,16 +5947,16 @@
         <v>17</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C64" s="6">
         <v>6</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>80</v>
@@ -5964,16 +5967,16 @@
         <v>17</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C65" s="6">
         <v>7</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F65" s="6" t="s">
         <v>100</v>
@@ -5984,16 +5987,16 @@
         <v>17</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C66" s="6">
         <v>8</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>80</v>
@@ -6004,13 +6007,13 @@
         <v>21</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C67" s="4">
         <v>1</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>103</v>
@@ -6024,16 +6027,16 @@
         <v>21</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C68" s="4">
         <v>2</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>80</v>
@@ -6044,16 +6047,16 @@
         <v>21</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C69" s="4">
         <v>3</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>80</v>
@@ -6064,16 +6067,16 @@
         <v>21</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C70" s="4">
         <v>4</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>100</v>
@@ -6084,13 +6087,13 @@
         <v>21</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C71" s="4">
         <v>5</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>79</v>
@@ -6104,13 +6107,13 @@
         <v>21</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C72" s="4">
         <v>1</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>93</v>
@@ -6124,13 +6127,13 @@
         <v>21</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C73" s="4">
         <v>2</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>120</v>
@@ -6144,16 +6147,16 @@
         <v>21</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C74" s="4">
         <v>3</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>80</v>
@@ -6164,13 +6167,13 @@
         <v>25</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C75" s="6">
         <v>1</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E75" s="5" t="s">
         <v>103</v>
@@ -6184,16 +6187,16 @@
         <v>25</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C76" s="6">
         <v>2</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>80</v>
@@ -6204,16 +6207,16 @@
         <v>25</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C77" s="6">
         <v>3</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F77" s="6" t="s">
         <v>80</v>
@@ -6224,16 +6227,16 @@
         <v>25</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C78" s="6">
         <v>4</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>100</v>
@@ -6244,13 +6247,13 @@
         <v>25</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C79" s="6">
         <v>5</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E79" s="5" t="s">
         <v>79</v>
@@ -6264,13 +6267,13 @@
         <v>25</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C80" s="6">
         <v>1</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E80" s="5" t="s">
         <v>93</v>
@@ -6284,13 +6287,13 @@
         <v>25</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C81" s="6">
         <v>2</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E81" s="5" t="s">
         <v>83</v>
@@ -6304,13 +6307,13 @@
         <v>25</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C82" s="6">
         <v>3</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E82" s="5" t="s">
         <v>86</v>
@@ -6324,13 +6327,13 @@
         <v>25</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C83" s="6">
         <v>4</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E83" s="5" t="s">
         <v>136</v>
@@ -6344,16 +6347,16 @@
         <v>25</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C84" s="6">
         <v>5</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>80</v>
@@ -6364,13 +6367,13 @@
         <v>25</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C85" s="6">
         <v>6</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>103</v>
@@ -6384,16 +6387,16 @@
         <v>25</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C86" s="6">
         <v>7</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>80</v>
@@ -6404,13 +6407,13 @@
         <v>28</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C87" s="4">
         <v>1</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>103</v>
@@ -6424,16 +6427,16 @@
         <v>28</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C88" s="4">
         <v>2</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>80</v>
@@ -6444,16 +6447,16 @@
         <v>28</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C89" s="4">
         <v>3</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F89" s="4" t="s">
         <v>80</v>
@@ -6464,16 +6467,16 @@
         <v>28</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C90" s="4">
         <v>4</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F90" s="4" t="s">
         <v>100</v>
@@ -6484,13 +6487,13 @@
         <v>28</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C91" s="4">
         <v>5</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>79</v>
@@ -6504,16 +6507,16 @@
         <v>28</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C92" s="4">
         <v>1</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F92" s="4" t="s">
         <v>80</v>
@@ -6524,13 +6527,13 @@
         <v>28</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C93" s="4">
         <v>2</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>93</v>
@@ -6544,13 +6547,13 @@
         <v>28</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C94" s="4">
         <v>3</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>93</v>
@@ -6564,13 +6567,13 @@
         <v>28</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C95" s="4">
         <v>4</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>89</v>
@@ -6584,13 +6587,13 @@
         <v>28</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C96" s="4">
         <v>5</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>83</v>
@@ -6604,13 +6607,13 @@
         <v>28</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C97" s="4">
         <v>6</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>86</v>
@@ -6624,13 +6627,13 @@
         <v>28</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C98" s="4">
         <v>7</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>103</v>
@@ -6644,13 +6647,13 @@
         <v>28</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C99" s="4">
         <v>8</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>103</v>
@@ -6664,13 +6667,13 @@
         <v>28</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C100" s="4">
         <v>9</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>103</v>
@@ -6684,13 +6687,13 @@
         <v>28</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C101" s="4">
         <v>10</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>103</v>
@@ -6704,13 +6707,13 @@
         <v>28</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C102" s="4">
         <v>11</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>93</v>
@@ -6724,13 +6727,13 @@
         <v>28</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C103" s="4">
         <v>12</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>103</v>
@@ -6744,16 +6747,16 @@
         <v>28</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C104" s="4">
         <v>13</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F104" s="4" t="s">
         <v>80</v>
@@ -6764,16 +6767,16 @@
         <v>28</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C105" s="4">
         <v>14</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F105" s="4" t="s">
         <v>80</v>
@@ -6784,13 +6787,13 @@
         <v>28</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C106" s="4">
         <v>1</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>86</v>
@@ -6804,16 +6807,16 @@
         <v>28</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C107" s="4">
         <v>2</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>80</v>
@@ -6824,16 +6827,16 @@
         <v>28</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C108" s="4">
         <v>3</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F108" s="4" t="s">
         <v>80</v>
@@ -6844,16 +6847,16 @@
         <v>28</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C109" s="4">
         <v>4</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F109" s="4" t="s">
         <v>80</v>
@@ -6864,16 +6867,16 @@
         <v>28</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C110" s="4">
         <v>5</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F110" s="4" t="s">
         <v>80</v>
@@ -6884,16 +6887,16 @@
         <v>28</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C111" s="4">
         <v>6</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F111" s="4" t="s">
         <v>80</v>
@@ -6904,13 +6907,13 @@
         <v>28</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C112" s="4">
         <v>7</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>103</v>
@@ -6924,16 +6927,16 @@
         <v>28</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C113" s="4">
         <v>8</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>100</v>
@@ -6944,13 +6947,13 @@
         <v>28</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C114" s="4">
         <v>9</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>103</v>
@@ -6964,13 +6967,13 @@
         <v>28</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C115" s="4">
         <v>10</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>103</v>
@@ -6984,16 +6987,16 @@
         <v>28</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C116" s="4">
         <v>11</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F116" s="4" t="s">
         <v>80</v>
@@ -7004,16 +7007,16 @@
         <v>28</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C117" s="4">
         <v>12</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F117" s="4" t="s">
         <v>80</v>
@@ -7024,13 +7027,13 @@
         <v>28</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C118" s="4">
         <v>1</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E118" s="3" t="s">
         <v>103</v>
@@ -7044,16 +7047,16 @@
         <v>28</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C119" s="4">
         <v>2</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F119" s="4" t="s">
         <v>80</v>
@@ -7064,13 +7067,13 @@
         <v>28</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C120" s="4">
         <v>3</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E120" s="3" t="s">
         <v>83</v>
@@ -7084,16 +7087,16 @@
         <v>28</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C121" s="4">
         <v>4</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F121" s="4" t="s">
         <v>80</v>
@@ -7104,16 +7107,16 @@
         <v>28</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C122" s="4">
         <v>5</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F122" s="4" t="s">
         <v>80</v>
@@ -7124,13 +7127,13 @@
         <v>28</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C123" s="4">
         <v>1</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E123" s="3" t="s">
         <v>89</v>
@@ -7144,13 +7147,13 @@
         <v>28</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C124" s="4">
         <v>2</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E124" s="3" t="s">
         <v>120</v>
@@ -7164,16 +7167,16 @@
         <v>28</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C125" s="4">
         <v>3</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F125" s="4" t="s">
         <v>80</v>
@@ -7184,13 +7187,13 @@
         <v>28</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C126" s="4">
         <v>4</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E126" s="3" t="s">
         <v>89</v>
@@ -7204,13 +7207,13 @@
         <v>28</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C127" s="4">
         <v>1</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E127" s="3" t="s">
         <v>89</v>
@@ -7224,13 +7227,13 @@
         <v>28</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C128" s="4">
         <v>2</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E128" s="3" t="s">
         <v>89</v>
@@ -7244,13 +7247,13 @@
         <v>28</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C129" s="4">
         <v>3</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E129" s="3" t="s">
         <v>120</v>
@@ -7264,13 +7267,13 @@
         <v>28</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C130" s="4">
         <v>4</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E130" s="3" t="s">
         <v>103</v>
@@ -7284,13 +7287,13 @@
         <v>28</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C131" s="4">
         <v>5</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E131" s="3" t="s">
         <v>103</v>
@@ -7304,13 +7307,13 @@
         <v>28</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C132" s="4">
         <v>6</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E132" s="3" t="s">
         <v>103</v>
@@ -7324,16 +7327,16 @@
         <v>28</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C133" s="4">
         <v>7</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F133" s="4" t="s">
         <v>80</v>
@@ -7344,16 +7347,16 @@
         <v>28</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C134" s="4">
         <v>8</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F134" s="4" t="s">
         <v>80</v>
@@ -7364,13 +7367,13 @@
         <v>31</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C135" s="6">
         <v>1</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E135" s="5" t="s">
         <v>103</v>
@@ -7384,16 +7387,16 @@
         <v>31</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C136" s="6">
         <v>2</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>80</v>
@@ -7404,16 +7407,16 @@
         <v>31</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C137" s="6">
         <v>3</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F137" s="6" t="s">
         <v>80</v>
@@ -7424,16 +7427,16 @@
         <v>31</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C138" s="6">
         <v>4</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>100</v>
@@ -7444,13 +7447,13 @@
         <v>31</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C139" s="6">
         <v>5</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E139" s="5" t="s">
         <v>79</v>
@@ -7464,13 +7467,13 @@
         <v>31</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C140" s="6">
         <v>1</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E140" s="5" t="s">
         <v>93</v>
@@ -7484,13 +7487,13 @@
         <v>31</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C141" s="6">
         <v>2</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E141" s="5" t="s">
         <v>136</v>
@@ -7504,16 +7507,16 @@
         <v>31</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C142" s="6">
         <v>3</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>80</v>
@@ -7524,13 +7527,13 @@
         <v>34</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C143" s="4">
         <v>1</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E143" s="3" t="s">
         <v>103</v>
@@ -7544,16 +7547,16 @@
         <v>34</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C144" s="4">
         <v>2</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F144" s="4" t="s">
         <v>80</v>
@@ -7564,16 +7567,16 @@
         <v>34</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C145" s="4">
         <v>3</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F145" s="4" t="s">
         <v>80</v>
@@ -7584,16 +7587,16 @@
         <v>34</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C146" s="4">
         <v>4</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F146" s="4" t="s">
         <v>100</v>
@@ -7604,13 +7607,13 @@
         <v>34</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C147" s="4">
         <v>5</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E147" s="3" t="s">
         <v>79</v>
@@ -7624,13 +7627,13 @@
         <v>34</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C148" s="4">
         <v>1</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E148" s="3" t="s">
         <v>93</v>
@@ -7644,13 +7647,13 @@
         <v>34</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C149" s="4">
         <v>2</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E149" s="3" t="s">
         <v>136</v>
@@ -7664,16 +7667,16 @@
         <v>34</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C150" s="4">
         <v>3</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F150" s="4" t="s">
         <v>80</v>
@@ -7684,13 +7687,13 @@
         <v>37</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C151" s="6">
         <v>1</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E151" s="5" t="s">
         <v>103</v>
@@ -7704,16 +7707,16 @@
         <v>37</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C152" s="6">
         <v>2</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>80</v>
@@ -7724,16 +7727,16 @@
         <v>37</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C153" s="6">
         <v>3</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F153" s="6" t="s">
         <v>80</v>
@@ -7744,16 +7747,16 @@
         <v>37</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C154" s="6">
         <v>4</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>100</v>
@@ -7764,13 +7767,13 @@
         <v>37</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C155" s="6">
         <v>5</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E155" s="5" t="s">
         <v>79</v>
@@ -7784,13 +7787,13 @@
         <v>37</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C156" s="6">
         <v>1</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E156" s="5" t="s">
         <v>93</v>
@@ -7804,13 +7807,13 @@
         <v>37</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C157" s="6">
         <v>2</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E157" s="5" t="s">
         <v>136</v>
@@ -7824,16 +7827,16 @@
         <v>37</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C158" s="6">
         <v>3</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>80</v>
@@ -7844,13 +7847,13 @@
         <v>40</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C159" s="4">
         <v>1</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E159" s="3" t="s">
         <v>103</v>
@@ -7864,16 +7867,16 @@
         <v>40</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C160" s="4">
         <v>2</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F160" s="4" t="s">
         <v>80</v>
@@ -7884,16 +7887,16 @@
         <v>40</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C161" s="4">
         <v>3</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F161" s="4" t="s">
         <v>80</v>
@@ -7904,16 +7907,16 @@
         <v>40</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C162" s="4">
         <v>4</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F162" s="4" t="s">
         <v>100</v>
@@ -7924,13 +7927,13 @@
         <v>40</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C163" s="4">
         <v>5</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E163" s="3" t="s">
         <v>79</v>
@@ -7944,13 +7947,13 @@
         <v>40</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C164" s="4">
         <v>1</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E164" s="3" t="s">
         <v>93</v>
@@ -7964,13 +7967,13 @@
         <v>40</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C165" s="4">
         <v>2</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E165" s="3" t="s">
         <v>93</v>
@@ -7984,13 +7987,13 @@
         <v>40</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C166" s="4">
         <v>3</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E166" s="3" t="s">
         <v>83</v>
@@ -8004,13 +8007,13 @@
         <v>40</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C167" s="4">
         <v>4</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E167" s="3" t="s">
         <v>86</v>
@@ -8024,13 +8027,13 @@
         <v>40</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C168" s="4">
         <v>5</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E168" s="3" t="s">
         <v>136</v>
@@ -8044,16 +8047,16 @@
         <v>40</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C169" s="4">
         <v>6</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F169" s="4" t="s">
         <v>80</v>
@@ -8064,13 +8067,13 @@
         <v>40</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C170" s="4">
         <v>7</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E170" s="3" t="s">
         <v>120</v>
@@ -8084,13 +8087,13 @@
         <v>40</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C171" s="4">
         <v>8</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E171" s="3" t="s">
         <v>120</v>
@@ -8104,16 +8107,16 @@
         <v>40</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C172" s="4">
         <v>9</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F172" s="4" t="s">
         <v>80</v>
@@ -8124,16 +8127,16 @@
         <v>40</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C173" s="4">
         <v>10</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F173" s="4" t="s">
         <v>80</v>
@@ -8144,16 +8147,16 @@
         <v>40</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C174" s="4">
         <v>11</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F174" s="4" t="s">
         <v>100</v>
@@ -8164,13 +8167,13 @@
         <v>43</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C175" s="6">
         <v>1</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E175" s="5" t="s">
         <v>103</v>
@@ -8184,16 +8187,16 @@
         <v>43</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C176" s="6">
         <v>2</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>80</v>
@@ -8204,16 +8207,16 @@
         <v>43</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C177" s="6">
         <v>3</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F177" s="6" t="s">
         <v>80</v>
@@ -8224,16 +8227,16 @@
         <v>43</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C178" s="6">
         <v>4</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>100</v>
@@ -8244,13 +8247,13 @@
         <v>43</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C179" s="6">
         <v>5</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E179" s="5" t="s">
         <v>79</v>
@@ -8264,13 +8267,13 @@
         <v>43</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C180" s="6">
         <v>1</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E180" s="5" t="s">
         <v>93</v>
@@ -8284,13 +8287,13 @@
         <v>43</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C181" s="6">
         <v>2</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E181" s="5" t="s">
         <v>93</v>
@@ -8304,13 +8307,13 @@
         <v>43</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C182" s="6">
         <v>3</v>
       </c>
       <c r="D182" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E182" s="5" t="s">
         <v>120</v>
@@ -8324,13 +8327,13 @@
         <v>43</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C183" s="6">
         <v>4</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E183" s="5" t="s">
         <v>120</v>
@@ -8344,16 +8347,16 @@
         <v>43</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C184" s="6">
         <v>5</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>80</v>
@@ -8364,16 +8367,16 @@
         <v>43</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C185" s="6">
         <v>6</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F185" s="6" t="s">
         <v>80</v>
@@ -8384,16 +8387,16 @@
         <v>43</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C186" s="6">
         <v>7</v>
       </c>
       <c r="D186" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>100</v>
@@ -8404,13 +8407,13 @@
         <v>43</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C187" s="6">
         <v>8</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E187" s="5" t="s">
         <v>83</v>
@@ -8424,13 +8427,13 @@
         <v>43</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C188" s="6">
         <v>9</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E188" s="5" t="s">
         <v>86</v>
@@ -8444,13 +8447,13 @@
         <v>43</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C189" s="6">
         <v>10</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E189" s="5" t="s">
         <v>136</v>
@@ -8464,16 +8467,16 @@
         <v>43</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C190" s="6">
         <v>11</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>80</v>
@@ -8484,16 +8487,16 @@
         <v>43</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C191" s="6">
         <v>12</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F191" s="6" t="s">
         <v>80</v>
@@ -8504,16 +8507,16 @@
         <v>43</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C192" s="6">
         <v>13</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>80</v>
@@ -8524,16 +8527,16 @@
         <v>43</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C193" s="6">
         <v>14</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E193" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F193" s="6" t="s">
         <v>80</v>
@@ -8544,16 +8547,16 @@
         <v>43</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C194" s="6">
         <v>15</v>
       </c>
       <c r="D194" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>80</v>
@@ -8564,13 +8567,13 @@
         <v>43</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C195" s="6">
         <v>1</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E195" s="5" t="s">
         <v>89</v>
@@ -8584,13 +8587,13 @@
         <v>43</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C196" s="6">
         <v>2</v>
       </c>
       <c r="D196" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E196" s="5" t="s">
         <v>120</v>
@@ -8604,16 +8607,16 @@
         <v>43</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C197" s="6">
         <v>3</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E197" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F197" s="6" t="s">
         <v>80</v>
@@ -8624,13 +8627,13 @@
         <v>43</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C198" s="6">
         <v>4</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E198" s="5" t="s">
         <v>89</v>
@@ -8644,13 +8647,13 @@
         <v>43</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C199" s="6">
         <v>1</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E199" s="5" t="s">
         <v>89</v>
@@ -8664,13 +8667,13 @@
         <v>43</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C200" s="6">
         <v>2</v>
       </c>
       <c r="D200" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E200" s="5" t="s">
         <v>89</v>
@@ -8684,13 +8687,13 @@
         <v>43</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C201" s="6">
         <v>3</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E201" s="5" t="s">
         <v>120</v>
@@ -8704,16 +8707,16 @@
         <v>43</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C202" s="6">
         <v>1</v>
       </c>
       <c r="D202" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>80</v>
@@ -8724,13 +8727,13 @@
         <v>43</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C203" s="6">
         <v>2</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E203" s="5" t="s">
         <v>103</v>
@@ -8744,16 +8747,16 @@
         <v>43</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C204" s="6">
         <v>3</v>
       </c>
       <c r="D204" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>80</v>
@@ -8764,16 +8767,16 @@
         <v>43</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C205" s="6">
         <v>4</v>
       </c>
       <c r="D205" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F205" s="6" t="s">
         <v>80</v>
@@ -8784,13 +8787,13 @@
         <v>46</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C206" s="4">
         <v>1</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E206" s="3" t="s">
         <v>103</v>
@@ -8804,16 +8807,16 @@
         <v>46</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C207" s="4">
         <v>2</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F207" s="4" t="s">
         <v>80</v>
@@ -8824,16 +8827,16 @@
         <v>46</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C208" s="4">
         <v>3</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F208" s="4" t="s">
         <v>80</v>
@@ -8844,16 +8847,16 @@
         <v>46</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C209" s="4">
         <v>4</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F209" s="4" t="s">
         <v>100</v>
@@ -8864,13 +8867,13 @@
         <v>46</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C210" s="4">
         <v>5</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E210" s="3" t="s">
         <v>79</v>
@@ -8884,13 +8887,13 @@
         <v>46</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C211" s="4">
         <v>1</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E211" s="3" t="s">
         <v>93</v>
@@ -8904,13 +8907,13 @@
         <v>46</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C212" s="4">
         <v>2</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E212" s="3" t="s">
         <v>136</v>
@@ -8924,16 +8927,16 @@
         <v>46</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C213" s="4">
         <v>3</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F213" s="4" t="s">
         <v>80</v>
@@ -8944,13 +8947,13 @@
         <v>49</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C214" s="6">
         <v>1</v>
       </c>
       <c r="D214" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E214" s="5" t="s">
         <v>103</v>
@@ -8964,16 +8967,16 @@
         <v>49</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C215" s="6">
         <v>2</v>
       </c>
       <c r="D215" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F215" s="6" t="s">
         <v>80</v>
@@ -8984,16 +8987,16 @@
         <v>49</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C216" s="6">
         <v>3</v>
       </c>
       <c r="D216" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E216" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>80</v>
@@ -9004,16 +9007,16 @@
         <v>49</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C217" s="6">
         <v>4</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F217" s="6" t="s">
         <v>100</v>
@@ -9024,13 +9027,13 @@
         <v>49</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C218" s="6">
         <v>5</v>
       </c>
       <c r="D218" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E218" s="5" t="s">
         <v>79</v>
@@ -9044,13 +9047,13 @@
         <v>49</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C219" s="6">
         <v>1</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E219" s="5" t="s">
         <v>93</v>
@@ -9064,13 +9067,13 @@
         <v>49</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C220" s="6">
         <v>2</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E220" s="5" t="s">
         <v>136</v>
@@ -9084,16 +9087,16 @@
         <v>49</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C221" s="6">
         <v>3</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F221" s="6" t="s">
         <v>80</v>
@@ -9104,13 +9107,13 @@
         <v>52</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C222" s="4">
         <v>1</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E222" s="3" t="s">
         <v>103</v>
@@ -9124,16 +9127,16 @@
         <v>52</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C223" s="4">
         <v>2</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F223" s="4" t="s">
         <v>80</v>
@@ -9144,16 +9147,16 @@
         <v>52</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C224" s="4">
         <v>3</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F224" s="4" t="s">
         <v>80</v>
@@ -9164,16 +9167,16 @@
         <v>52</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C225" s="4">
         <v>4</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F225" s="4" t="s">
         <v>100</v>
@@ -9184,13 +9187,13 @@
         <v>52</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C226" s="4">
         <v>5</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E226" s="3" t="s">
         <v>79</v>
@@ -9204,13 +9207,13 @@
         <v>52</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C227" s="4">
         <v>1</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E227" s="3" t="s">
         <v>93</v>
@@ -9224,13 +9227,13 @@
         <v>52</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C228" s="4">
         <v>2</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E228" s="3" t="s">
         <v>136</v>
@@ -9244,16 +9247,16 @@
         <v>52</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C229" s="4">
         <v>3</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F229" s="4" t="s">
         <v>80</v>
@@ -9264,13 +9267,13 @@
         <v>55</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C230" s="6">
         <v>1</v>
       </c>
       <c r="D230" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E230" s="5" t="s">
         <v>103</v>
@@ -9284,16 +9287,16 @@
         <v>55</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C231" s="6">
         <v>2</v>
       </c>
       <c r="D231" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E231" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F231" s="6" t="s">
         <v>80</v>
@@ -9304,16 +9307,16 @@
         <v>55</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C232" s="6">
         <v>3</v>
       </c>
       <c r="D232" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E232" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F232" s="6" t="s">
         <v>80</v>
@@ -9324,16 +9327,16 @@
         <v>55</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C233" s="6">
         <v>4</v>
       </c>
       <c r="D233" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E233" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F233" s="6" t="s">
         <v>100</v>
@@ -9344,13 +9347,13 @@
         <v>55</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C234" s="6">
         <v>5</v>
       </c>
       <c r="D234" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E234" s="5" t="s">
         <v>79</v>
@@ -9364,13 +9367,13 @@
         <v>55</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C235" s="6">
         <v>1</v>
       </c>
       <c r="D235" s="5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E235" s="5" t="s">
         <v>93</v>
@@ -9384,16 +9387,16 @@
         <v>55</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C236" s="6">
         <v>2</v>
       </c>
       <c r="D236" s="5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E236" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F236" s="6" t="s">
         <v>80</v>
@@ -9404,16 +9407,16 @@
         <v>55</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C237" s="6">
         <v>3</v>
       </c>
       <c r="D237" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E237" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F237" s="6" t="s">
         <v>100</v>
@@ -9424,16 +9427,16 @@
         <v>55</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C238" s="6">
         <v>4</v>
       </c>
       <c r="D238" s="5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E238" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F238" s="6" t="s">
         <v>80</v>
@@ -9444,16 +9447,16 @@
         <v>55</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C239" s="6">
         <v>5</v>
       </c>
       <c r="D239" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E239" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F239" s="6" t="s">
         <v>100</v>
@@ -9464,16 +9467,16 @@
         <v>55</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C240" s="6">
         <v>6</v>
       </c>
       <c r="D240" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="E240" s="5" t="s">
         <v>270</v>
-      </c>
-      <c r="E240" s="5" t="s">
-        <v>269</v>
       </c>
       <c r="F240" s="6" t="s">
         <v>100</v>
@@ -9484,13 +9487,13 @@
         <v>58</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C241" s="4">
         <v>1</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E241" s="3" t="s">
         <v>103</v>
@@ -9504,16 +9507,16 @@
         <v>58</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C242" s="4">
         <v>2</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F242" s="4" t="s">
         <v>80</v>
@@ -9524,16 +9527,16 @@
         <v>58</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C243" s="4">
         <v>3</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F243" s="4" t="s">
         <v>80</v>
@@ -9544,16 +9547,16 @@
         <v>58</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C244" s="4">
         <v>4</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F244" s="4" t="s">
         <v>100</v>
@@ -9564,13 +9567,13 @@
         <v>58</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C245" s="4">
         <v>5</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E245" s="3" t="s">
         <v>79</v>
@@ -9584,13 +9587,13 @@
         <v>58</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C246" s="4">
         <v>1</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E246" s="3" t="s">
         <v>83</v>
@@ -9604,13 +9607,13 @@
         <v>58</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C247" s="4">
         <v>2</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E247" s="3" t="s">
         <v>120</v>
@@ -9624,16 +9627,16 @@
         <v>58</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C248" s="4">
         <v>3</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F248" s="4" t="s">
         <v>80</v>
@@ -9644,13 +9647,13 @@
         <v>58</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C249" s="4">
         <v>4</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E249" s="3" t="s">
         <v>103</v>
@@ -9664,16 +9667,16 @@
         <v>58</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C250" s="4">
         <v>5</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F250" s="4" t="s">
         <v>100</v>
@@ -9684,16 +9687,16 @@
         <v>58</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C251" s="4">
         <v>6</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F251" s="4" t="s">
         <v>80</v>
@@ -9704,13 +9707,13 @@
         <v>58</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C252" s="4">
         <v>1</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E252" s="3" t="s">
         <v>83</v>
@@ -9724,16 +9727,16 @@
         <v>58</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C253" s="4">
         <v>2</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F253" s="4" t="s">
         <v>100</v>
@@ -9744,16 +9747,16 @@
         <v>58</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C254" s="4">
         <v>3</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E254" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F254" s="4" t="s">
         <v>80</v>
@@ -9764,13 +9767,13 @@
         <v>61</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C255" s="6">
         <v>1</v>
       </c>
       <c r="D255" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E255" s="5" t="s">
         <v>103</v>
@@ -9784,16 +9787,16 @@
         <v>61</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C256" s="6">
         <v>2</v>
       </c>
       <c r="D256" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E256" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F256" s="6" t="s">
         <v>80</v>
@@ -9804,16 +9807,16 @@
         <v>61</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C257" s="6">
         <v>3</v>
       </c>
       <c r="D257" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E257" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F257" s="6" t="s">
         <v>80</v>
@@ -9824,16 +9827,16 @@
         <v>61</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C258" s="6">
         <v>4</v>
       </c>
       <c r="D258" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E258" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F258" s="6" t="s">
         <v>100</v>
@@ -9844,13 +9847,13 @@
         <v>61</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C259" s="6">
         <v>5</v>
       </c>
       <c r="D259" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E259" s="5" t="s">
         <v>79</v>
@@ -9864,13 +9867,13 @@
         <v>61</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C260" s="6">
         <v>1</v>
       </c>
       <c r="D260" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E260" s="5" t="s">
         <v>83</v>
@@ -9884,16 +9887,16 @@
         <v>61</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C261" s="6">
         <v>2</v>
       </c>
       <c r="D261" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E261" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F261" s="6" t="s">
         <v>80</v>
@@ -9904,13 +9907,13 @@
         <v>64</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C262" s="4">
         <v>1</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E262" s="3" t="s">
         <v>103</v>
@@ -9924,16 +9927,16 @@
         <v>64</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C263" s="4">
         <v>2</v>
       </c>
       <c r="D263" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E263" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F263" s="4" t="s">
         <v>80</v>
@@ -9944,16 +9947,16 @@
         <v>64</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C264" s="4">
         <v>3</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E264" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F264" s="4" t="s">
         <v>80</v>
@@ -9964,16 +9967,16 @@
         <v>64</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C265" s="4">
         <v>4</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E265" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F265" s="4" t="s">
         <v>100</v>
@@ -9984,13 +9987,13 @@
         <v>64</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C266" s="4">
         <v>5</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E266" s="3" t="s">
         <v>79</v>
@@ -10004,13 +10007,13 @@
         <v>64</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C267" s="4">
         <v>1</v>
       </c>
       <c r="D267" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E267" s="3" t="s">
         <v>83</v>
@@ -10024,16 +10027,16 @@
         <v>64</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C268" s="4">
         <v>2</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E268" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F268" s="4" t="s">
         <v>80</v>
@@ -10044,13 +10047,13 @@
         <v>67</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C269" s="6">
         <v>1</v>
       </c>
       <c r="D269" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E269" s="5" t="s">
         <v>103</v>
@@ -10064,16 +10067,16 @@
         <v>67</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C270" s="6">
         <v>2</v>
       </c>
       <c r="D270" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E270" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F270" s="6" t="s">
         <v>80</v>
@@ -10084,16 +10087,16 @@
         <v>67</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C271" s="6">
         <v>3</v>
       </c>
       <c r="D271" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E271" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F271" s="6" t="s">
         <v>80</v>
@@ -10104,16 +10107,16 @@
         <v>67</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C272" s="6">
         <v>4</v>
       </c>
       <c r="D272" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E272" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F272" s="6" t="s">
         <v>100</v>
@@ -10124,13 +10127,13 @@
         <v>67</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C273" s="6">
         <v>5</v>
       </c>
       <c r="D273" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E273" s="5" t="s">
         <v>79</v>
@@ -10159,32 +10162,32 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>75</v>
@@ -10192,13 +10195,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>75</v>
@@ -10206,13 +10209,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>75</v>
@@ -10220,55 +10223,55 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>297</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>75</v>
@@ -10276,69 +10279,69 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>75</v>
@@ -10346,167 +10349,167 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>75</v>
@@ -10514,13 +10517,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>75</v>
@@ -10528,153 +10531,153 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>372</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>75</v>
@@ -10682,58 +10685,58 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -10758,12 +10761,12 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -10772,13 +10775,13 @@
         <v>3</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -10786,7 +10789,7 @@
         <v>77</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>4</v>
@@ -10794,7 +10797,7 @@
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -10803,7 +10806,7 @@
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>78</v>
@@ -10812,7 +10815,7 @@
         <v>79</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -10821,7 +10824,7 @@
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>82</v>
@@ -10830,7 +10833,7 @@
         <v>83</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -10839,7 +10842,7 @@
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>85</v>
@@ -10848,7 +10851,7 @@
         <v>86</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -10857,7 +10860,7 @@
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>88</v>
@@ -10866,7 +10869,7 @@
         <v>89</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -10875,16 +10878,16 @@
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>103</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -10893,16 +10896,16 @@
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -10911,16 +10914,16 @@
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -10929,16 +10932,16 @@
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>103</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -10947,16 +10950,16 @@
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>120</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -10965,16 +10968,16 @@
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>103</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -10983,16 +10986,16 @@
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -11001,16 +11004,16 @@
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>103</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -11019,16 +11022,16 @@
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>103</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -11037,16 +11040,16 @@
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -11055,16 +11058,16 @@
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -11072,7 +11075,7 @@
         <v>91</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4</v>
@@ -11080,7 +11083,7 @@
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -11089,7 +11092,7 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>92</v>
@@ -11098,7 +11101,7 @@
         <v>93</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -11107,7 +11110,7 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>82</v>
@@ -11116,7 +11119,7 @@
         <v>83</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -11125,16 +11128,16 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>103</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -11143,16 +11146,16 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -11161,16 +11164,16 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>83</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -11179,16 +11182,16 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -11197,16 +11200,16 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -11214,7 +11217,7 @@
         <v>96</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>4</v>
@@ -11222,7 +11225,7 @@
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -11231,7 +11234,7 @@
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>92</v>
@@ -11240,7 +11243,7 @@
         <v>93</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -11249,7 +11252,7 @@
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>82</v>
@@ -11258,7 +11261,7 @@
         <v>83</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -11267,16 +11270,16 @@
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>89</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -11285,16 +11288,16 @@
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>120</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -11303,16 +11306,16 @@
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -11321,16 +11324,16 @@
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>89</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -11338,7 +11341,7 @@
         <v>97</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>4</v>
@@ -11346,7 +11349,7 @@
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
       <c r="F34" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -11355,7 +11358,7 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>92</v>
@@ -11364,7 +11367,7 @@
         <v>93</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -11373,7 +11376,7 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>82</v>
@@ -11382,7 +11385,7 @@
         <v>83</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -11391,7 +11394,7 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>99</v>
@@ -11400,7 +11403,7 @@
         <v>93</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -11409,7 +11412,7 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>102</v>
@@ -11418,7 +11421,7 @@
         <v>103</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -11427,7 +11430,7 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>105</v>
@@ -11436,7 +11439,7 @@
         <v>103</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -11445,7 +11448,7 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>107</v>
@@ -11454,7 +11457,7 @@
         <v>103</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -11463,7 +11466,7 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>109</v>
@@ -11472,7 +11475,7 @@
         <v>103</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -11481,7 +11484,7 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>111</v>
@@ -11490,7 +11493,7 @@
         <v>103</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -11499,7 +11502,7 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>113</v>
@@ -11508,7 +11511,7 @@
         <v>103</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -11517,7 +11520,7 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>115</v>
@@ -11526,7 +11529,7 @@
         <v>103</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -11535,7 +11538,7 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>117</v>
@@ -11544,7 +11547,7 @@
         <v>103</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -11553,16 +11556,16 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E46" s="5" t="s">
         <v>89</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -11571,16 +11574,16 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>89</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -11589,16 +11592,16 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>120</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -11607,16 +11610,16 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>103</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -11625,16 +11628,16 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>103</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -11643,16 +11646,16 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>103</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -11661,16 +11664,16 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -11679,16 +11682,16 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
   </sheetData>

--- a/docs/baseline/output/05_검진_예약접수_SP계약서.xlsx
+++ b/docs/baseline/output/05_검진_예약접수_SP계약서.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2433" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2468" uniqueCount="477">
   <si>
     <t>외부 호출 Stored Procedure 20개</t>
   </si>
@@ -801,6 +801,12 @@
   </si>
   <si>
     <t>허용여부</t>
+  </si>
+  <si>
+    <t>RS5 추가검사구성</t>
+  </si>
+  <si>
+    <t>선택여부</t>
   </si>
   <si>
     <t>RS1 변경이력</t>
@@ -4686,7 +4692,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F273"/>
+  <dimension ref="A1:F280"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -8783,142 +8789,142 @@
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A206" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B206" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C206" s="4">
+      <c r="A206" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B206" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="C206" s="6">
         <v>1</v>
       </c>
-      <c r="D206" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="E206" s="3" t="s">
+      <c r="D206" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="E206" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F206" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A207" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B207" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="C207" s="6">
+        <v>2</v>
+      </c>
+      <c r="D207" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="E207" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F207" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A208" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B208" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="C208" s="6">
+        <v>3</v>
+      </c>
+      <c r="D208" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="E208" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F208" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A209" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B209" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="C209" s="6">
+        <v>4</v>
+      </c>
+      <c r="D209" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="E209" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="F206" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A207" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B207" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C207" s="4">
-        <v>2</v>
-      </c>
-      <c r="D207" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E207" s="3" t="s">
+      <c r="F209" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A210" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B210" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="C210" s="6">
+        <v>5</v>
+      </c>
+      <c r="D210" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E210" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F210" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A211" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="C211" s="6">
+        <v>6</v>
+      </c>
+      <c r="D211" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="E211" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="F207" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A208" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B208" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C208" s="4">
-        <v>3</v>
-      </c>
-      <c r="D208" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E208" s="3" t="s">
+      <c r="F211" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A212" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B212" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="C212" s="6">
+        <v>7</v>
+      </c>
+      <c r="D212" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="E212" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="F208" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A209" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B209" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C209" s="4">
-        <v>4</v>
-      </c>
-      <c r="D209" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E209" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="F209" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A210" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B210" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C210" s="4">
-        <v>5</v>
-      </c>
-      <c r="D210" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E210" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="F210" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A211" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B211" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C211" s="4">
-        <v>1</v>
-      </c>
-      <c r="D211" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="E211" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F211" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A212" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B212" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C212" s="4">
-        <v>2</v>
-      </c>
-      <c r="D212" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="E212" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="F212" s="4" t="s">
+      <c r="F212" s="6" t="s">
         <v>80</v>
       </c>
     </row>
@@ -8927,158 +8933,158 @@
         <v>46</v>
       </c>
       <c r="B213" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C213" s="4">
+        <v>1</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E213" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F213" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A214" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C214" s="4">
+        <v>2</v>
+      </c>
+      <c r="D214" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E214" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F214" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A215" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C215" s="4">
+        <v>3</v>
+      </c>
+      <c r="D215" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E215" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F215" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A216" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C216" s="4">
+        <v>4</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E216" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F216" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A217" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C217" s="4">
+        <v>5</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E217" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F217" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A218" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B218" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="C213" s="4">
+      <c r="C218" s="4">
+        <v>1</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E218" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F218" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A219" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C219" s="4">
+        <v>2</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E219" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F219" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A220" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C220" s="4">
         <v>3</v>
       </c>
-      <c r="D213" s="3" t="s">
+      <c r="D220" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E213" s="3" t="s">
+      <c r="E220" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="F213" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A214" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B214" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="C214" s="6">
-        <v>1</v>
-      </c>
-      <c r="D214" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="E214" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="F214" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A215" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B215" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="C215" s="6">
-        <v>2</v>
-      </c>
-      <c r="D215" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="E215" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="F215" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A216" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B216" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="C216" s="6">
-        <v>3</v>
-      </c>
-      <c r="D216" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="E216" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="F216" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A217" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B217" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="C217" s="6">
-        <v>4</v>
-      </c>
-      <c r="D217" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="E217" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="F217" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A218" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B218" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="C218" s="6">
-        <v>5</v>
-      </c>
-      <c r="D218" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="E218" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="F218" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A219" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B219" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="C219" s="6">
-        <v>1</v>
-      </c>
-      <c r="D219" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="E219" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="F219" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A220" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B220" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="C220" s="6">
-        <v>2</v>
-      </c>
-      <c r="D220" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="E220" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="F220" s="6" t="s">
+      <c r="F220" s="4" t="s">
         <v>80</v>
       </c>
     </row>
@@ -9087,158 +9093,158 @@
         <v>49</v>
       </c>
       <c r="B221" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C221" s="6">
+        <v>1</v>
+      </c>
+      <c r="D221" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="E221" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F221" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A222" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B222" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C222" s="6">
+        <v>2</v>
+      </c>
+      <c r="D222" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E222" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="F222" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A223" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C223" s="6">
+        <v>3</v>
+      </c>
+      <c r="D223" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="E223" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F223" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A224" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C224" s="6">
+        <v>4</v>
+      </c>
+      <c r="D224" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E224" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="F224" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A225" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C225" s="6">
+        <v>5</v>
+      </c>
+      <c r="D225" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="E225" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F225" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A226" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B226" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="C221" s="6">
+      <c r="C226" s="6">
+        <v>1</v>
+      </c>
+      <c r="D226" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="E226" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F226" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A227" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C227" s="6">
+        <v>2</v>
+      </c>
+      <c r="D227" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E227" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="F227" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A228" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C228" s="6">
         <v>3</v>
       </c>
-      <c r="D221" s="5" t="s">
+      <c r="D228" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="E221" s="5" t="s">
+      <c r="E228" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="F221" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A222" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B222" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C222" s="4">
-        <v>1</v>
-      </c>
-      <c r="D222" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="E222" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F222" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A223" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B223" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C223" s="4">
-        <v>2</v>
-      </c>
-      <c r="D223" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E223" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="F223" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A224" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B224" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C224" s="4">
-        <v>3</v>
-      </c>
-      <c r="D224" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E224" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="F224" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A225" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B225" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C225" s="4">
-        <v>4</v>
-      </c>
-      <c r="D225" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E225" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="F225" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A226" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B226" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C226" s="4">
-        <v>5</v>
-      </c>
-      <c r="D226" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E226" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="F226" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A227" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B227" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C227" s="4">
-        <v>1</v>
-      </c>
-      <c r="D227" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="E227" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F227" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A228" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B228" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C228" s="4">
-        <v>2</v>
-      </c>
-      <c r="D228" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="E228" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="F228" s="4" t="s">
+      <c r="F228" s="6" t="s">
         <v>80</v>
       </c>
     </row>
@@ -9247,158 +9253,158 @@
         <v>52</v>
       </c>
       <c r="B229" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C229" s="4">
+        <v>1</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E229" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F229" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A230" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C230" s="4">
+        <v>2</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E230" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F230" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A231" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C231" s="4">
+        <v>3</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E231" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F231" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A232" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C232" s="4">
+        <v>4</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E232" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F232" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A233" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C233" s="4">
+        <v>5</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E233" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F233" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A234" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B234" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="C229" s="4">
+      <c r="C234" s="4">
+        <v>1</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E234" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F234" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A235" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B235" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C235" s="4">
+        <v>2</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E235" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F235" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A236" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C236" s="4">
         <v>3</v>
       </c>
-      <c r="D229" s="3" t="s">
+      <c r="D236" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E229" s="3" t="s">
+      <c r="E236" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="F229" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A230" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B230" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="C230" s="6">
-        <v>1</v>
-      </c>
-      <c r="D230" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="E230" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="F230" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A231" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B231" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="C231" s="6">
-        <v>2</v>
-      </c>
-      <c r="D231" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="E231" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="F231" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A232" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B232" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="C232" s="6">
-        <v>3</v>
-      </c>
-      <c r="D232" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="E232" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="F232" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A233" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B233" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="C233" s="6">
-        <v>4</v>
-      </c>
-      <c r="D233" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="E233" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="F233" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A234" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B234" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="C234" s="6">
-        <v>5</v>
-      </c>
-      <c r="D234" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="E234" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="F234" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A235" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B235" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="C235" s="6">
-        <v>1</v>
-      </c>
-      <c r="D235" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="E235" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="F235" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A236" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B236" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="C236" s="6">
-        <v>2</v>
-      </c>
-      <c r="D236" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="E236" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="F236" s="6" t="s">
+      <c r="F236" s="4" t="s">
         <v>80</v>
       </c>
     </row>
@@ -9407,19 +9413,19 @@
         <v>55</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>262</v>
+        <v>171</v>
       </c>
       <c r="C237" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D237" s="5" t="s">
-        <v>266</v>
+        <v>172</v>
       </c>
       <c r="E237" s="5" t="s">
-        <v>158</v>
+        <v>103</v>
       </c>
       <c r="F237" s="6" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -9427,16 +9433,16 @@
         <v>55</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>262</v>
+        <v>171</v>
       </c>
       <c r="C238" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D238" s="5" t="s">
-        <v>267</v>
+        <v>173</v>
       </c>
       <c r="E238" s="5" t="s">
-        <v>268</v>
+        <v>174</v>
       </c>
       <c r="F238" s="6" t="s">
         <v>80</v>
@@ -9447,19 +9453,19 @@
         <v>55</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>262</v>
+        <v>171</v>
       </c>
       <c r="C239" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D239" s="5" t="s">
-        <v>269</v>
+        <v>175</v>
       </c>
       <c r="E239" s="5" t="s">
-        <v>270</v>
+        <v>176</v>
       </c>
       <c r="F239" s="6" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -9467,159 +9473,159 @@
         <v>55</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>262</v>
+        <v>171</v>
       </c>
       <c r="C240" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D240" s="5" t="s">
-        <v>271</v>
+        <v>177</v>
       </c>
       <c r="E240" s="5" t="s">
-        <v>270</v>
+        <v>178</v>
       </c>
       <c r="F240" s="6" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A241" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B241" s="3" t="s">
+      <c r="A241" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B241" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C241" s="4">
+      <c r="C241" s="6">
+        <v>5</v>
+      </c>
+      <c r="D241" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="E241" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F241" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A242" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B242" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C242" s="6">
         <v>1</v>
       </c>
-      <c r="D241" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="E241" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F241" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A242" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B242" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C242" s="4">
+      <c r="D242" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E242" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F242" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A243" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B243" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C243" s="6">
         <v>2</v>
       </c>
-      <c r="D242" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E242" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="F242" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A243" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B243" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C243" s="4">
+      <c r="D243" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="E243" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="F243" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A244" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B244" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C244" s="6">
         <v>3</v>
       </c>
-      <c r="D243" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E243" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="F243" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A244" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B244" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C244" s="4">
+      <c r="D244" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="E244" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="F244" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A245" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B245" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C245" s="6">
         <v>4</v>
       </c>
-      <c r="D244" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E244" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="F244" s="4" t="s">
+      <c r="D245" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="E245" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="F245" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A246" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B246" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C246" s="6">
+        <v>5</v>
+      </c>
+      <c r="D246" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="E246" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="F246" s="6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A245" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B245" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C245" s="4">
-        <v>5</v>
-      </c>
-      <c r="D245" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E245" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="F245" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A246" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B246" s="3" t="s">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A247" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B247" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C247" s="6">
+        <v>6</v>
+      </c>
+      <c r="D247" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="E247" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="C246" s="4">
-        <v>1</v>
-      </c>
-      <c r="D246" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="E246" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F246" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A247" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B247" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="C247" s="4">
-        <v>2</v>
-      </c>
-      <c r="D247" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="E247" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F247" s="4" t="s">
-        <v>80</v>
+      <c r="F247" s="6" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -9627,16 +9633,16 @@
         <v>58</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>272</v>
+        <v>171</v>
       </c>
       <c r="C248" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>274</v>
+        <v>172</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="F248" s="4" t="s">
         <v>80</v>
@@ -9647,16 +9653,16 @@
         <v>58</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>272</v>
+        <v>171</v>
       </c>
       <c r="C249" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>275</v>
+        <v>173</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>103</v>
+        <v>174</v>
       </c>
       <c r="F249" s="4" t="s">
         <v>80</v>
@@ -9667,19 +9673,19 @@
         <v>58</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>272</v>
+        <v>171</v>
       </c>
       <c r="C250" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="F250" s="4" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -9687,19 +9693,19 @@
         <v>58</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>272</v>
+        <v>171</v>
       </c>
       <c r="C251" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>143</v>
+        <v>178</v>
       </c>
       <c r="F251" s="4" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -9707,19 +9713,19 @@
         <v>58</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>276</v>
+        <v>171</v>
       </c>
       <c r="C252" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>277</v>
+        <v>179</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F252" s="4" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -9727,19 +9733,19 @@
         <v>58</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C253" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>174</v>
+        <v>83</v>
       </c>
       <c r="F253" s="4" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -9747,398 +9753,538 @@
         <v>58</v>
       </c>
       <c r="B254" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C254" s="4">
+        <v>2</v>
+      </c>
+      <c r="D254" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E254" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="F254" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A255" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B255" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C255" s="4">
+        <v>3</v>
+      </c>
+      <c r="D255" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C254" s="4">
+      <c r="E255" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F255" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A256" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B256" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C256" s="4">
+        <v>4</v>
+      </c>
+      <c r="D256" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="E256" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F256" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A257" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B257" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C257" s="4">
+        <v>5</v>
+      </c>
+      <c r="D257" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E257" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F257" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A258" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B258" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C258" s="4">
+        <v>6</v>
+      </c>
+      <c r="D258" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E258" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F258" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A259" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B259" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C259" s="4">
+        <v>1</v>
+      </c>
+      <c r="D259" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="E259" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F259" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A260" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B260" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C260" s="4">
+        <v>2</v>
+      </c>
+      <c r="D260" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E260" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F260" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A261" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B261" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C261" s="4">
         <v>3</v>
       </c>
-      <c r="D254" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="E254" s="3" t="s">
+      <c r="D261" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="E261" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="F254" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A255" s="5" t="s">
+      <c r="F261" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A262" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B255" s="5" t="s">
+      <c r="B262" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C255" s="6">
+      <c r="C262" s="6">
         <v>1</v>
       </c>
-      <c r="D255" s="5" t="s">
+      <c r="D262" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="E255" s="5" t="s">
+      <c r="E262" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="F255" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A256" s="5" t="s">
+      <c r="F262" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A263" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B256" s="5" t="s">
+      <c r="B263" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C256" s="6">
+      <c r="C263" s="6">
         <v>2</v>
       </c>
-      <c r="D256" s="5" t="s">
+      <c r="D263" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="E256" s="5" t="s">
+      <c r="E263" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="F256" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A257" s="5" t="s">
+      <c r="F263" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A264" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B257" s="5" t="s">
+      <c r="B264" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C257" s="6">
+      <c r="C264" s="6">
         <v>3</v>
       </c>
-      <c r="D257" s="5" t="s">
+      <c r="D264" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="E257" s="5" t="s">
+      <c r="E264" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="F257" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A258" s="5" t="s">
+      <c r="F264" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A265" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B258" s="5" t="s">
+      <c r="B265" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C258" s="6">
+      <c r="C265" s="6">
         <v>4</v>
       </c>
-      <c r="D258" s="5" t="s">
+      <c r="D265" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="E258" s="5" t="s">
+      <c r="E265" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="F258" s="6" t="s">
+      <c r="F265" s="6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A259" s="5" t="s">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A266" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B259" s="5" t="s">
+      <c r="B266" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C259" s="6">
+      <c r="C266" s="6">
         <v>5</v>
       </c>
-      <c r="D259" s="5" t="s">
+      <c r="D266" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="E259" s="5" t="s">
+      <c r="E266" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="F259" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A260" s="5" t="s">
+      <c r="F266" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A267" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B260" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="C260" s="6">
+      <c r="B267" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="C267" s="6">
         <v>1</v>
       </c>
-      <c r="D260" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="E260" s="5" t="s">
+      <c r="D267" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="E267" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="F260" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A261" s="5" t="s">
+      <c r="F267" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A268" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B261" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="C261" s="6">
+      <c r="B268" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="C268" s="6">
         <v>2</v>
       </c>
-      <c r="D261" s="5" t="s">
+      <c r="D268" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="E261" s="5" t="s">
+      <c r="E268" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="F261" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A262" s="3" t="s">
+      <c r="F268" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A269" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B262" s="3" t="s">
+      <c r="B269" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C262" s="4">
+      <c r="C269" s="4">
         <v>1</v>
       </c>
-      <c r="D262" s="3" t="s">
+      <c r="D269" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="E262" s="3" t="s">
+      <c r="E269" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="F262" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A263" s="3" t="s">
+      <c r="F269" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A270" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B263" s="3" t="s">
+      <c r="B270" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C263" s="4">
+      <c r="C270" s="4">
         <v>2</v>
       </c>
-      <c r="D263" s="3" t="s">
+      <c r="D270" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="E263" s="3" t="s">
+      <c r="E270" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="F263" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A264" s="3" t="s">
+      <c r="F270" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A271" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B264" s="3" t="s">
+      <c r="B271" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C264" s="4">
+      <c r="C271" s="4">
         <v>3</v>
       </c>
-      <c r="D264" s="3" t="s">
+      <c r="D271" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="E264" s="3" t="s">
+      <c r="E271" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="F264" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A265" s="3" t="s">
+      <c r="F271" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A272" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B265" s="3" t="s">
+      <c r="B272" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C265" s="4">
+      <c r="C272" s="4">
         <v>4</v>
       </c>
-      <c r="D265" s="3" t="s">
+      <c r="D272" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="E265" s="3" t="s">
+      <c r="E272" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="F265" s="4" t="s">
+      <c r="F272" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A266" s="3" t="s">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A273" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B266" s="3" t="s">
+      <c r="B273" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C266" s="4">
+      <c r="C273" s="4">
         <v>5</v>
       </c>
-      <c r="D266" s="3" t="s">
+      <c r="D273" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="E266" s="3" t="s">
+      <c r="E273" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F266" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A267" s="3" t="s">
+      <c r="F273" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A274" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B267" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="C267" s="4">
+      <c r="B274" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C274" s="4">
         <v>1</v>
       </c>
-      <c r="D267" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="E267" s="3" t="s">
+      <c r="D274" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="E274" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="F267" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A268" s="3" t="s">
+      <c r="F274" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A275" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B268" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="C268" s="4">
+      <c r="B275" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C275" s="4">
         <v>2</v>
       </c>
-      <c r="D268" s="3" t="s">
+      <c r="D275" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E268" s="3" t="s">
+      <c r="E275" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="F268" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A269" s="5" t="s">
+      <c r="F275" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A276" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B269" s="5" t="s">
+      <c r="B276" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C269" s="6">
+      <c r="C276" s="6">
         <v>1</v>
       </c>
-      <c r="D269" s="5" t="s">
+      <c r="D276" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="E269" s="5" t="s">
+      <c r="E276" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="F269" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A270" s="5" t="s">
+      <c r="F276" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A277" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B270" s="5" t="s">
+      <c r="B277" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C270" s="6">
+      <c r="C277" s="6">
         <v>2</v>
       </c>
-      <c r="D270" s="5" t="s">
+      <c r="D277" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="E270" s="5" t="s">
+      <c r="E277" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="F270" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A271" s="5" t="s">
+      <c r="F277" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A278" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B271" s="5" t="s">
+      <c r="B278" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C271" s="6">
+      <c r="C278" s="6">
         <v>3</v>
       </c>
-      <c r="D271" s="5" t="s">
+      <c r="D278" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="E271" s="5" t="s">
+      <c r="E278" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="F271" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A272" s="5" t="s">
+      <c r="F278" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A279" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B272" s="5" t="s">
+      <c r="B279" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C272" s="6">
+      <c r="C279" s="6">
         <v>4</v>
       </c>
-      <c r="D272" s="5" t="s">
+      <c r="D279" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="E272" s="5" t="s">
+      <c r="E279" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="F272" s="6" t="s">
+      <c r="F279" s="6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A273" s="5" t="s">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A280" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B273" s="5" t="s">
+      <c r="B280" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C273" s="6">
+      <c r="C280" s="6">
         <v>5</v>
       </c>
-      <c r="D273" s="5" t="s">
+      <c r="D280" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="E273" s="5" t="s">
+      <c r="E280" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="F273" s="6" t="s">
+      <c r="F280" s="6" t="s">
         <v>80</v>
       </c>
     </row>
@@ -10162,7 +10308,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -10170,24 +10316,24 @@
         <v>173</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>75</v>
@@ -10195,13 +10341,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>75</v>
@@ -10209,13 +10355,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>75</v>
@@ -10223,55 +10369,55 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>299</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>75</v>
@@ -10279,27 +10425,27 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>193</v>
@@ -10307,13 +10453,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>194</v>
@@ -10321,13 +10467,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>195</v>
@@ -10335,13 +10481,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>75</v>
@@ -10349,13 +10495,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>196</v>
@@ -10363,13 +10509,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>196</v>
@@ -10377,13 +10523,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>194</v>
@@ -10391,13 +10537,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>214</v>
@@ -10405,13 +10551,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>214</v>
@@ -10419,13 +10565,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>214</v>
@@ -10433,13 +10579,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>215</v>
@@ -10447,13 +10593,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>215</v>
@@ -10461,13 +10607,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>215</v>
@@ -10475,13 +10621,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>193</v>
@@ -10489,13 +10635,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>215</v>
@@ -10503,13 +10649,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>75</v>
@@ -10517,13 +10663,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>75</v>
@@ -10531,13 +10677,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>214</v>
@@ -10545,13 +10691,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>214</v>
@@ -10559,55 +10705,55 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>374</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>213</v>
@@ -10615,13 +10761,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>193</v>
@@ -10629,13 +10775,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>213</v>
@@ -10643,13 +10789,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>213</v>
@@ -10657,13 +10803,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>209</v>
@@ -10671,13 +10817,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>75</v>
@@ -10685,58 +10831,58 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -10761,12 +10907,12 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -10775,7 +10921,7 @@
         <v>3</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>74</v>
@@ -10789,7 +10935,7 @@
         <v>77</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>4</v>
@@ -10797,7 +10943,7 @@
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -10806,7 +10952,7 @@
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>78</v>
@@ -10815,7 +10961,7 @@
         <v>79</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -10824,7 +10970,7 @@
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>82</v>
@@ -10833,7 +10979,7 @@
         <v>83</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -10842,7 +10988,7 @@
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>85</v>
@@ -10851,7 +10997,7 @@
         <v>86</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -10860,7 +11006,7 @@
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>88</v>
@@ -10869,7 +11015,7 @@
         <v>89</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -10878,7 +11024,7 @@
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>189</v>
@@ -10887,7 +11033,7 @@
         <v>103</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -10896,16 +11042,16 @@
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>174</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -10914,16 +11060,16 @@
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>176</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -10932,7 +11078,7 @@
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>187</v>
@@ -10941,7 +11087,7 @@
         <v>103</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -10950,7 +11096,7 @@
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>183</v>
@@ -10959,7 +11105,7 @@
         <v>120</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -10968,7 +11114,7 @@
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>234</v>
@@ -10977,7 +11123,7 @@
         <v>103</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -10986,7 +11132,7 @@
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>235</v>
@@ -10995,7 +11141,7 @@
         <v>185</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -11004,7 +11150,7 @@
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>236</v>
@@ -11013,7 +11159,7 @@
         <v>103</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -11022,16 +11168,16 @@
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>103</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -11040,7 +11186,7 @@
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>242</v>
@@ -11049,7 +11195,7 @@
         <v>174</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -11058,7 +11204,7 @@
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>243</v>
@@ -11067,7 +11213,7 @@
         <v>176</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -11075,7 +11221,7 @@
         <v>91</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4</v>
@@ -11083,7 +11229,7 @@
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -11092,7 +11238,7 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>92</v>
@@ -11101,7 +11247,7 @@
         <v>93</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -11110,7 +11256,7 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>82</v>
@@ -11119,7 +11265,7 @@
         <v>83</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -11128,7 +11274,7 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>239</v>
@@ -11137,7 +11283,7 @@
         <v>103</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -11146,7 +11292,7 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>240</v>
@@ -11155,7 +11301,7 @@
         <v>174</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -11164,7 +11310,7 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>241</v>
@@ -11173,7 +11319,7 @@
         <v>83</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -11182,7 +11328,7 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>242</v>
@@ -11191,7 +11337,7 @@
         <v>174</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -11200,7 +11346,7 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>243</v>
@@ -11209,7 +11355,7 @@
         <v>176</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -11217,7 +11363,7 @@
         <v>96</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>4</v>
@@ -11225,7 +11371,7 @@
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -11234,7 +11380,7 @@
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>92</v>
@@ -11243,7 +11389,7 @@
         <v>93</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -11252,7 +11398,7 @@
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>82</v>
@@ -11261,7 +11407,7 @@
         <v>83</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -11270,7 +11416,7 @@
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>245</v>
@@ -11279,7 +11425,7 @@
         <v>89</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -11288,7 +11434,7 @@
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>246</v>
@@ -11297,7 +11443,7 @@
         <v>120</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -11306,7 +11452,7 @@
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>247</v>
@@ -11315,7 +11461,7 @@
         <v>221</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -11324,7 +11470,7 @@
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>248</v>
@@ -11333,7 +11479,7 @@
         <v>89</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -11341,7 +11487,7 @@
         <v>97</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>4</v>
@@ -11349,7 +11495,7 @@
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
       <c r="F34" s="5" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -11358,7 +11504,7 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>92</v>
@@ -11367,7 +11513,7 @@
         <v>93</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -11376,7 +11522,7 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>82</v>
@@ -11385,7 +11531,7 @@
         <v>83</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -11394,7 +11540,7 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>99</v>
@@ -11403,7 +11549,7 @@
         <v>93</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -11412,7 +11558,7 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>102</v>
@@ -11421,7 +11567,7 @@
         <v>103</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -11430,7 +11576,7 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>105</v>
@@ -11439,7 +11585,7 @@
         <v>103</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -11448,7 +11594,7 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>107</v>
@@ -11457,7 +11603,7 @@
         <v>103</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -11466,7 +11612,7 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>109</v>
@@ -11475,7 +11621,7 @@
         <v>103</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -11484,7 +11630,7 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>111</v>
@@ -11493,7 +11639,7 @@
         <v>103</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -11502,7 +11648,7 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>113</v>
@@ -11511,7 +11657,7 @@
         <v>103</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -11520,7 +11666,7 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>115</v>
@@ -11529,7 +11675,7 @@
         <v>103</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -11538,7 +11684,7 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>117</v>
@@ -11547,7 +11693,7 @@
         <v>103</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -11556,7 +11702,7 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>250</v>
@@ -11565,7 +11711,7 @@
         <v>89</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -11574,7 +11720,7 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>245</v>
@@ -11583,7 +11729,7 @@
         <v>89</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -11592,7 +11738,7 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>246</v>
@@ -11601,7 +11747,7 @@
         <v>120</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -11610,7 +11756,7 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>251</v>
@@ -11619,7 +11765,7 @@
         <v>103</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -11628,7 +11774,7 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>252</v>
@@ -11637,7 +11783,7 @@
         <v>103</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -11646,7 +11792,7 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>237</v>
@@ -11655,7 +11801,7 @@
         <v>103</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -11664,7 +11810,7 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>242</v>
@@ -11673,7 +11819,7 @@
         <v>174</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -11682,7 +11828,7 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>243</v>
@@ -11691,7 +11837,7 @@
         <v>176</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
   </sheetData>
